--- a/data/Prices of basic commodities in Gaza/commodity-prices-in-gaza.xlsx
+++ b/data/Prices of basic commodities in Gaza/commodity-prices-in-gaza.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="217">
   <si>
     <t>أرز حبة طويلة الياسمين تايلند - 1 كغم</t>
   </si>
@@ -677,6 +677,12 @@
   </si>
   <si>
     <t>Monthly Percent Change % (November - December 2025)</t>
+  </si>
+  <si>
+    <t>Monthly Percent Change % ( December 2025 - January 2026)</t>
+  </si>
+  <si>
+    <t>Monthly Percent Change % (January 2026 - February 2026)</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:BI48"/>
+  <dimension ref="A2:BM48"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" style="5" customWidth="1"/>
@@ -1118,12 +1124,12 @@
     <col min="9" max="9" width="12.42578125" style="5" customWidth="1"/>
     <col min="10" max="10" width="19.140625" style="5" customWidth="1"/>
     <col min="11" max="11" width="18.42578125" style="5" customWidth="1"/>
-    <col min="12" max="60" width="20.85546875" style="5" customWidth="1"/>
-    <col min="61" max="61" width="20.42578125" style="5" customWidth="1"/>
-    <col min="62" max="16384" width="8.85546875" style="5"/>
+    <col min="12" max="64" width="20.85546875" style="5" customWidth="1"/>
+    <col min="65" max="65" width="20.42578125" style="5" customWidth="1"/>
+    <col min="66" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:61" s="1" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="1" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>98</v>
       </c>
@@ -1301,11 +1307,23 @@
       <c r="BH2" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BI2" s="3">
+        <v>46023</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="BK2" s="3">
+        <v>46054</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="BM2" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>136</v>
       </c>
@@ -1513,12 +1531,26 @@
         <f>(BG3/BE3*100-100)/100</f>
         <v>-6.3063063063064112E-2</v>
       </c>
-      <c r="BI3" s="8">
-        <f>(BG3/F3*100-100)/100</f>
-        <v>-0.57630000905471701</v>
+      <c r="BI3" s="13">
+        <v>6.2740453845771835</v>
+      </c>
+      <c r="BJ3" s="7">
+        <f>(BI3/BG3*100-100)/100</f>
+        <v>0.9162976219364225</v>
+      </c>
+      <c r="BK3" s="13">
+        <v>9.2740453845771817</v>
+      </c>
+      <c r="BL3" s="7">
+        <f>(BK3/BI3*100-100)/100</f>
+        <v>0.47816039191788096</v>
+      </c>
+      <c r="BM3" s="8">
+        <f>(BK3/F3*100-100)/100</f>
+        <v>0.20017057918057632</v>
       </c>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>137</v>
       </c>
@@ -1726,12 +1758,26 @@
         <f t="shared" ref="BH4:BH48" si="16">(BG4/BE4*100-100)/100</f>
         <v>-0.42587601078167092</v>
       </c>
-      <c r="BI4" s="8">
-        <f t="shared" ref="BI4:BI44" si="17">(BG4/F4*100-100)/100</f>
-        <v>1.5524158381302016E-2</v>
+      <c r="BI4" s="13">
+        <v>60.79595959595963</v>
+      </c>
+      <c r="BJ4" s="7">
+        <f t="shared" ref="BJ4:BJ48" si="17">(BI4/BG4*100-100)/100</f>
+        <v>-0.3421254801536493</v>
+      </c>
+      <c r="BK4" s="13">
+        <v>62.169934640522911</v>
+      </c>
+      <c r="BL4" s="7">
+        <f t="shared" ref="BL4:BL48" si="18">(BK4/BI4*100-100)/100</f>
+        <v>2.2599775605064848E-2</v>
+      </c>
+      <c r="BM4" s="8">
+        <f t="shared" ref="BM4:BM44" si="19">(BK4/F4*100-100)/100</f>
+        <v>-0.31681390504919876</v>
       </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>138</v>
       </c>
@@ -1939,12 +1985,26 @@
         <f t="shared" si="16"/>
         <v>-0.17184265010352007</v>
       </c>
-      <c r="BI5" s="8">
+      <c r="BI5" s="13">
+        <v>6</v>
+      </c>
+      <c r="BJ5" s="7">
         <f t="shared" si="17"/>
-        <v>-0.28571428571428598</v>
+        <v>0.20000000000000043</v>
+      </c>
+      <c r="BK5" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="BL5" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.25</v>
+      </c>
+      <c r="BM5" s="8">
+        <f t="shared" si="19"/>
+        <v>-0.3571428571428571</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>139</v>
       </c>
@@ -2152,12 +2212,26 @@
         <f t="shared" si="16"/>
         <v>-0.2645228758169938</v>
       </c>
-      <c r="BI6" s="8">
+      <c r="BI6" s="13">
+        <v>22.537037037037027</v>
+      </c>
+      <c r="BJ6" s="7">
         <f t="shared" si="17"/>
-        <v>0.6574754901960782</v>
+        <v>-0.15017457383446314</v>
+      </c>
+      <c r="BK6" s="13">
+        <v>24.233333333333341</v>
+      </c>
+      <c r="BL6" s="7">
+        <f t="shared" si="18"/>
+        <v>7.5267050123254645E-2</v>
+      </c>
+      <c r="BM6" s="8">
+        <f t="shared" si="19"/>
+        <v>0.51458333333333373</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>140</v>
       </c>
@@ -2365,12 +2439,26 @@
         <f t="shared" si="16"/>
         <v>-0.47397660818713427</v>
       </c>
-      <c r="BI7" s="8">
+      <c r="BI7" s="13">
+        <v>24.071428571428594</v>
+      </c>
+      <c r="BJ7" s="7">
         <f t="shared" si="17"/>
-        <v>2.5506578947368426</v>
+        <v>-0.49154292067021332</v>
+      </c>
+      <c r="BK7" s="13">
+        <v>30</v>
+      </c>
+      <c r="BL7" s="7">
+        <f t="shared" si="18"/>
+        <v>0.24629080118694247</v>
+      </c>
+      <c r="BM7" s="8">
+        <f t="shared" si="19"/>
+        <v>1.25</v>
       </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>141</v>
       </c>
@@ -2578,12 +2666,26 @@
         <f t="shared" si="16"/>
         <v>-6.3620386643234786E-2</v>
       </c>
-      <c r="BI8" s="8">
+      <c r="BI8" s="13">
+        <v>25.453530166880601</v>
+      </c>
+      <c r="BJ8" s="7">
         <f t="shared" si="17"/>
-        <v>-0.19183585568542696</v>
+        <v>3.6036036036035883E-2</v>
+      </c>
+      <c r="BK8" s="13">
+        <v>23.340786556190917</v>
+      </c>
+      <c r="BL8" s="7">
+        <f t="shared" si="18"/>
+        <v>-8.3003952569169565E-2</v>
+      </c>
+      <c r="BM8" s="8">
+        <f t="shared" si="19"/>
+        <v>-0.23221096854635134</v>
       </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>142</v>
       </c>
@@ -2791,12 +2893,26 @@
         <f t="shared" si="16"/>
         <v>-0.3345238095238095</v>
       </c>
-      <c r="BI9" s="8">
+      <c r="BI9" s="13">
+        <v>6.7727272727272743</v>
+      </c>
+      <c r="BJ9" s="7">
         <f t="shared" si="17"/>
-        <v>1.3972125435540059</v>
+        <v>0.10253699788583574</v>
+      </c>
+      <c r="BK9" s="13">
+        <v>6.4545454545454595</v>
+      </c>
+      <c r="BL9" s="7">
+        <f t="shared" si="18"/>
+        <v>-4.6979865771811548E-2</v>
+      </c>
+      <c r="BM9" s="8">
+        <f t="shared" si="19"/>
+        <v>1.5188470066518867</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>143</v>
       </c>
@@ -3004,12 +3120,26 @@
         <f t="shared" si="16"/>
         <v>-0.12814256137237492</v>
       </c>
-      <c r="BI10" s="8">
+      <c r="BI10" s="13">
+        <v>10.742424242424248</v>
+      </c>
+      <c r="BJ10" s="7">
         <f t="shared" si="17"/>
-        <v>1.2148962148962135</v>
+        <v>-5.111757041193812E-3</v>
+      </c>
+      <c r="BK10" s="13">
+        <v>10.03055555555556</v>
+      </c>
+      <c r="BL10" s="7">
+        <f t="shared" si="18"/>
+        <v>-6.6267042783262731E-2</v>
+      </c>
+      <c r="BM10" s="8">
+        <f t="shared" si="19"/>
+        <v>1.0575498575498585</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>144</v>
       </c>
@@ -3217,12 +3347,26 @@
         <f t="shared" si="16"/>
         <v>8.3333333333332996E-2</v>
       </c>
-      <c r="BI11" s="8">
+      <c r="BI11" s="13">
+        <v>11.33333333333333</v>
+      </c>
+      <c r="BJ11" s="7">
         <f t="shared" si="17"/>
-        <v>1.2891304347826091</v>
+        <v>-9.8132320354545749E-3</v>
+      </c>
+      <c r="BK11" s="13">
+        <v>10</v>
+      </c>
+      <c r="BL11" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.11764705882352927</v>
+      </c>
+      <c r="BM11" s="8">
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>145</v>
       </c>
@@ -3430,12 +3574,26 @@
         <f t="shared" si="16"/>
         <v>-0.33280590717299602</v>
       </c>
-      <c r="BI12" s="8">
+      <c r="BI12" s="13">
+        <v>9.5454545454545432</v>
+      </c>
+      <c r="BJ12" s="7">
         <f t="shared" si="17"/>
-        <v>1.4731182795698925</v>
+        <v>-3.9525691699607533E-3</v>
+      </c>
+      <c r="BK12" s="13">
+        <v>11</v>
+      </c>
+      <c r="BL12" s="7">
+        <f t="shared" si="18"/>
+        <v>0.1523809523809527</v>
+      </c>
+      <c r="BM12" s="8">
+        <f t="shared" si="19"/>
+        <v>1.838709677419355</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>146</v>
       </c>
@@ -3643,12 +3801,26 @@
         <f t="shared" si="16"/>
         <v>-0.37056567593480305</v>
       </c>
-      <c r="BI13" s="8">
+      <c r="BI13" s="13">
+        <v>8.3636363636363669</v>
+      </c>
+      <c r="BJ13" s="7">
         <f t="shared" si="17"/>
-        <v>5.4126984126984148</v>
+        <v>0.15931593159315938</v>
+      </c>
+      <c r="BK13" s="13">
+        <v>9.2727272727272751</v>
+      </c>
+      <c r="BL13" s="7">
+        <f t="shared" si="18"/>
+        <v>0.10869565217391283</v>
+      </c>
+      <c r="BM13" s="8">
+        <f t="shared" si="19"/>
+        <v>7.242424242424244</v>
       </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>147</v>
       </c>
@@ -3856,12 +4028,26 @@
         <f t="shared" si="16"/>
         <v>-0.53679653679653694</v>
       </c>
-      <c r="BI14" s="8">
+      <c r="BI14" s="13">
+        <v>30.090909090909097</v>
+      </c>
+      <c r="BJ14" s="7">
         <f t="shared" si="17"/>
-        <v>3.0761904761904746</v>
+        <v>0.9685641461342408</v>
+      </c>
+      <c r="BK14" s="13">
+        <v>21.083333333333336</v>
+      </c>
+      <c r="BL14" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.29934541792547847</v>
+      </c>
+      <c r="BM14" s="8">
+        <f t="shared" si="19"/>
+        <v>4.6222222222222227</v>
       </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>148</v>
       </c>
@@ -4069,12 +4255,26 @@
         <f t="shared" si="16"/>
         <v>0.40176991150442432</v>
       </c>
-      <c r="BI15" s="8">
+      <c r="BI15" s="13">
+        <v>19.75</v>
+      </c>
+      <c r="BJ15" s="7">
         <f t="shared" si="17"/>
-        <v>2.5999999999999979</v>
+        <v>0.37152777777777857</v>
+      </c>
+      <c r="BK15" s="13">
+        <v>15.333333333333327</v>
+      </c>
+      <c r="BL15" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.22362869198312268</v>
+      </c>
+      <c r="BM15" s="8">
+        <f t="shared" si="19"/>
+        <v>2.8333333333333313</v>
       </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>149</v>
       </c>
@@ -4282,12 +4482,26 @@
         <f t="shared" si="16"/>
         <v>-0.23404255319148887</v>
       </c>
-      <c r="BI16" s="8">
+      <c r="BI16" s="13">
+        <v>6.7272727272727266</v>
+      </c>
+      <c r="BJ16" s="7">
         <f t="shared" si="17"/>
-        <v>4.3169230769230804</v>
+        <v>-0.19023569023569081</v>
+      </c>
+      <c r="BK16" s="13">
+        <v>8.3333333333333357</v>
+      </c>
+      <c r="BL16" s="7">
+        <f t="shared" si="18"/>
+        <v>0.23873873873873919</v>
+      </c>
+      <c r="BM16" s="8">
+        <f t="shared" si="19"/>
+        <v>4.3333333333333348</v>
       </c>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>150</v>
       </c>
@@ -4495,12 +4709,26 @@
         <f t="shared" si="16"/>
         <v>-0.36947791164658617</v>
       </c>
-      <c r="BI17" s="8">
+      <c r="BI17" s="13">
+        <v>3.318181818181817</v>
+      </c>
+      <c r="BJ17" s="7">
         <f t="shared" si="17"/>
-        <v>-0.16710875331564964</v>
+        <v>9.9015634047480608E-2</v>
+      </c>
+      <c r="BK17" s="13">
+        <v>3.211538461538463</v>
+      </c>
+      <c r="BL17" s="7">
+        <f t="shared" si="18"/>
+        <v>-3.2139093782928542E-2</v>
+      </c>
+      <c r="BM17" s="8">
+        <f t="shared" si="19"/>
+        <v>-0.11405835543766543</v>
       </c>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>151</v>
       </c>
@@ -4708,12 +4936,26 @@
         <f t="shared" si="16"/>
         <v>-0.36434108527131737</v>
       </c>
-      <c r="BI18" s="8">
+      <c r="BI18" s="13">
+        <v>3.7727272727272698</v>
+      </c>
+      <c r="BJ18" s="7">
         <f t="shared" si="17"/>
-        <v>0.2307692307692315</v>
+        <v>0.19623059866962136</v>
+      </c>
+      <c r="BK18" s="13">
+        <v>4.0833333333333313</v>
+      </c>
+      <c r="BL18" s="7">
+        <f t="shared" si="18"/>
+        <v>8.2329317269076649E-2</v>
+      </c>
+      <c r="BM18" s="8">
+        <f t="shared" si="19"/>
+        <v>0.59349593495934871</v>
       </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>152</v>
       </c>
@@ -4921,12 +5163,26 @@
         <f t="shared" si="16"/>
         <v>-0.2</v>
       </c>
-      <c r="BI19" s="8">
+      <c r="BI19" s="13">
+        <v>4</v>
+      </c>
+      <c r="BJ19" s="7">
         <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BK19" s="13">
+        <v>4</v>
+      </c>
+      <c r="BL19" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BM19" s="8">
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>153</v>
       </c>
@@ -5134,12 +5390,26 @@
         <f t="shared" si="16"/>
         <v>-0.34367541766109766</v>
       </c>
-      <c r="BI20" s="8">
+      <c r="BI20" s="13">
+        <v>86.666666666666686</v>
+      </c>
+      <c r="BJ20" s="7">
         <f t="shared" si="17"/>
-        <v>12.500245459008347</v>
+        <v>-5.4545454545454536E-2</v>
+      </c>
+      <c r="BK20" s="13">
+        <v>73.07692307692308</v>
+      </c>
+      <c r="BL20" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.15680473372781079</v>
+      </c>
+      <c r="BM20" s="8">
+        <f t="shared" si="19"/>
+        <v>9.762433442845813</v>
       </c>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>154</v>
       </c>
@@ -5347,12 +5617,26 @@
         <f t="shared" si="16"/>
         <v>1.1111111111111285E-2</v>
       </c>
-      <c r="BI21" s="8">
+      <c r="BI21" s="13">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="BJ21" s="7">
         <f t="shared" si="17"/>
-        <v>5.0092449922958391</v>
+        <v>-0.15897435897435913</v>
+      </c>
+      <c r="BK21" s="13">
+        <v>28.94444444444445</v>
+      </c>
+      <c r="BL21" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.11754742547425451</v>
+      </c>
+      <c r="BM21" s="8">
+        <f t="shared" si="19"/>
+        <v>3.4598527649375113</v>
       </c>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>155</v>
       </c>
@@ -5560,12 +5844,26 @@
         <f t="shared" si="16"/>
         <v>-0.9</v>
       </c>
-      <c r="BI22" s="8">
+      <c r="BI22" s="13">
+        <v>10</v>
+      </c>
+      <c r="BJ22" s="7">
         <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BK22" s="13">
+        <v>10</v>
+      </c>
+      <c r="BL22" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BM22" s="8">
+        <f t="shared" si="19"/>
         <v>1.5</v>
       </c>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>156</v>
       </c>
@@ -5773,12 +6071,26 @@
         <f t="shared" si="16"/>
         <v>-0.88</v>
       </c>
-      <c r="BI23" s="8">
+      <c r="BI23" s="13">
+        <v>18</v>
+      </c>
+      <c r="BJ23" s="7">
         <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BK23" s="13">
+        <v>18</v>
+      </c>
+      <c r="BL23" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BM23" s="8">
+        <f t="shared" si="19"/>
         <v>1.25</v>
       </c>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>157</v>
       </c>
@@ -5986,12 +6298,26 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BI24" s="8">
+      <c r="BI24" s="13">
+        <v>28</v>
+      </c>
+      <c r="BJ24" s="7">
         <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BK24" s="13">
+        <v>28</v>
+      </c>
+      <c r="BL24" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BM24" s="8">
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>158</v>
       </c>
@@ -6199,12 +6525,26 @@
         <f t="shared" si="16"/>
         <v>-0.125</v>
       </c>
-      <c r="BI25" s="8">
+      <c r="BI25" s="13">
+        <v>7</v>
+      </c>
+      <c r="BJ25" s="7">
         <f t="shared" si="17"/>
-        <v>0.75</v>
+        <v>0</v>
+      </c>
+      <c r="BK25" s="13">
+        <v>6.4285714285714333</v>
+      </c>
+      <c r="BL25" s="7">
+        <f t="shared" si="18"/>
+        <v>-8.1632653061223831E-2</v>
+      </c>
+      <c r="BM25" s="8">
+        <f t="shared" si="19"/>
+        <v>0.60714285714285832</v>
       </c>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>159</v>
       </c>
@@ -6412,12 +6752,26 @@
         <f t="shared" si="16"/>
         <v>-0.5757575757575758</v>
       </c>
-      <c r="BI26" s="8">
+      <c r="BI26" s="13">
+        <v>7</v>
+      </c>
+      <c r="BJ26" s="7">
         <f t="shared" si="17"/>
-        <v>-0.20707964601769915</v>
+        <v>0</v>
+      </c>
+      <c r="BK26" s="13">
+        <v>6</v>
+      </c>
+      <c r="BL26" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="BM26" s="8">
+        <f t="shared" si="19"/>
+        <v>-0.32035398230088502</v>
       </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>160</v>
       </c>
@@ -6625,12 +6979,26 @@
         <f t="shared" si="16"/>
         <v>-0.21819389110225784</v>
       </c>
-      <c r="BI27" s="8">
+      <c r="BI27" s="13">
+        <v>120.67730380983389</v>
+      </c>
+      <c r="BJ27" s="7">
         <f t="shared" si="17"/>
-        <v>2.4068692368191127</v>
+        <v>-0.22235434007134372</v>
+      </c>
+      <c r="BK27" s="13">
+        <v>129.6925152346839</v>
+      </c>
+      <c r="BL27" s="7">
+        <f t="shared" si="18"/>
+        <v>7.4705111402359414E-2</v>
+      </c>
+      <c r="BM27" s="8">
+        <f t="shared" si="19"/>
+        <v>1.8472560973585928</v>
       </c>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>161</v>
       </c>
@@ -6838,12 +7206,26 @@
         <f t="shared" si="16"/>
         <v>-0.21819389110225784</v>
       </c>
-      <c r="BI28" s="8">
+      <c r="BI28" s="13">
+        <v>133.54954954954954</v>
+      </c>
+      <c r="BJ28" s="7">
         <f t="shared" si="17"/>
-        <v>2.0606368744982602</v>
+        <v>-0.22235434007134358</v>
+      </c>
+      <c r="BK28" s="13">
+        <v>143.52638352638351</v>
+      </c>
+      <c r="BL28" s="7">
+        <f t="shared" si="18"/>
+        <v>7.4705111402359137E-2</v>
+      </c>
+      <c r="BM28" s="8">
+        <f t="shared" si="19"/>
+        <v>1.5578959440345574</v>
       </c>
     </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>162</v>
       </c>
@@ -7051,12 +7433,26 @@
         <f t="shared" si="16"/>
         <v>0.47398843930635848</v>
       </c>
-      <c r="BI29" s="8">
+      <c r="BI29" s="13">
+        <v>41.35820895522388</v>
+      </c>
+      <c r="BJ29" s="7">
         <f t="shared" si="17"/>
-        <v>0.17692307692307679</v>
+        <v>-2.6865671641791097E-2</v>
+      </c>
+      <c r="BK29" s="13">
+        <v>42.046908315565027</v>
+      </c>
+      <c r="BL29" s="7">
+        <f t="shared" si="18"/>
+        <v>1.6652059596844709E-2</v>
+      </c>
+      <c r="BM29" s="8">
+        <f t="shared" si="19"/>
+        <v>0.16437592258487754</v>
       </c>
     </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>163</v>
       </c>
@@ -7264,12 +7660,26 @@
         <f t="shared" si="16"/>
         <v>0.48051948051948129</v>
       </c>
-      <c r="BI30" s="8">
+      <c r="BI30" s="13">
+        <v>5.400000000000003</v>
+      </c>
+      <c r="BJ30" s="7">
         <f t="shared" si="17"/>
-        <v>0.33847702113384825</v>
+        <v>4.2105263157894798E-2</v>
+      </c>
+      <c r="BK30" s="13">
+        <v>5.2916666666666652</v>
+      </c>
+      <c r="BL30" s="7">
+        <f t="shared" si="18"/>
+        <v>-2.0061728395062629E-2</v>
+      </c>
+      <c r="BM30" s="8">
+        <f t="shared" si="19"/>
+        <v>0.36685116851168459</v>
       </c>
     </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>164</v>
       </c>
@@ -7477,12 +7887,26 @@
         <f t="shared" si="16"/>
         <v>-0.15151515151515141</v>
       </c>
-      <c r="BI31" s="8">
+      <c r="BI31" s="13">
+        <v>41.250000000000007</v>
+      </c>
+      <c r="BJ31" s="7">
         <f t="shared" si="17"/>
-        <v>0.16189989785495412</v>
+        <v>-2.7472527472528442E-3</v>
+      </c>
+      <c r="BK31" s="13">
+        <v>39.545454545454554</v>
+      </c>
+      <c r="BL31" s="7">
+        <f t="shared" si="18"/>
+        <v>-4.1322314049586736E-2</v>
+      </c>
+      <c r="BM31" s="8">
+        <f t="shared" si="19"/>
+        <v>0.11082737487231896</v>
       </c>
     </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>165</v>
       </c>
@@ -7690,12 +8114,26 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BI32" s="8">
+      <c r="BI32" s="13">
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="BJ32" s="7">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>5.5555555555555573E-2</v>
+      </c>
+      <c r="BK32" s="13">
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="BL32" s="7">
+        <f t="shared" si="18"/>
+        <v>-9.7744360902255634E-2</v>
+      </c>
+      <c r="BM32" s="8">
+        <f t="shared" si="19"/>
+        <v>0.90476190476190477</v>
       </c>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>166</v>
       </c>
@@ -7903,12 +8341,26 @@
         <f t="shared" si="16"/>
         <v>-0.1594202898550722</v>
       </c>
-      <c r="BI33" s="8">
+      <c r="BI33" s="13">
+        <v>6.1666666666666714</v>
+      </c>
+      <c r="BJ33" s="7">
         <f t="shared" si="17"/>
-        <v>0.14336917562724152</v>
+        <v>-4.3103448275862488E-2</v>
+      </c>
+      <c r="BK33" s="13">
+        <v>6</v>
+      </c>
+      <c r="BL33" s="7">
+        <f t="shared" si="18"/>
+        <v>-2.7027027027027799E-2</v>
+      </c>
+      <c r="BM33" s="8">
+        <f t="shared" si="19"/>
+        <v>6.4516129032257938E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>167</v>
       </c>
@@ -8050,7 +8502,7 @@
         <v>128</v>
       </c>
       <c r="AP34" s="7">
-        <f t="shared" ref="AP34:AP48" si="18">(AO34/AM34*100-100)/100</f>
+        <f t="shared" ref="AP34:AP48" si="20">(AO34/AM34*100-100)/100</f>
         <v>0.55017301038062272</v>
       </c>
       <c r="AQ34" s="13">
@@ -8116,12 +8568,26 @@
         <f t="shared" si="16"/>
         <v>1.138790035587192E-2</v>
       </c>
-      <c r="BI34" s="8">
+      <c r="BI34" s="13">
+        <v>88.75</v>
+      </c>
+      <c r="BJ34" s="7">
         <f t="shared" si="17"/>
-        <v>0.92979890310786117</v>
+        <v>9.2980295566502211E-2</v>
+      </c>
+      <c r="BK34" s="13">
+        <v>86.200000000000031</v>
+      </c>
+      <c r="BL34" s="7">
+        <f t="shared" si="18"/>
+        <v>-2.8732394366196842E-2</v>
+      </c>
+      <c r="BM34" s="8">
+        <f t="shared" si="19"/>
+        <v>1.0486288848263259</v>
       </c>
     </row>
-    <row r="35" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>168</v>
       </c>
@@ -8263,7 +8729,7 @@
         <v>1.4250000000000005</v>
       </c>
       <c r="AP35" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-0.30434782608695615</v>
       </c>
       <c r="AQ35" s="13">
@@ -8329,12 +8795,26 @@
         <f t="shared" si="16"/>
         <v>-0.11111111111111044</v>
       </c>
-      <c r="BI35" s="8">
+      <c r="BI35" s="13">
+        <v>2.850000000000001</v>
+      </c>
+      <c r="BJ35" s="7">
         <f t="shared" si="17"/>
-        <v>-0.22479999999999961</v>
+        <v>0</v>
+      </c>
+      <c r="BK35" s="13">
+        <v>1.4250000000000005</v>
+      </c>
+      <c r="BL35" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.5</v>
+      </c>
+      <c r="BM35" s="8">
+        <f t="shared" si="19"/>
+        <v>-0.61239999999999983</v>
       </c>
     </row>
-    <row r="36" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>169</v>
       </c>
@@ -8476,7 +8956,7 @@
         <v>1.3458333333333319</v>
       </c>
       <c r="AP36" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.27956989247311709</v>
       </c>
       <c r="AQ36" s="13">
@@ -8542,12 +9022,26 @@
         <f t="shared" si="16"/>
         <v>-6.0606060606062332E-3</v>
       </c>
-      <c r="BI36" s="8">
+      <c r="BI36" s="13">
+        <v>2.4535714285714265</v>
+      </c>
+      <c r="BJ36" s="7">
         <f t="shared" si="17"/>
-        <v>0.18336081017428157</v>
+        <v>-7.6104896387310536E-2</v>
+      </c>
+      <c r="BK36" s="13">
+        <v>2.2087499999999984</v>
+      </c>
+      <c r="BL36" s="7">
+        <f t="shared" si="18"/>
+        <v>-9.9781659388646207E-2</v>
+      </c>
+      <c r="BM36" s="8">
+        <f t="shared" si="19"/>
+        <v>-1.5790155440415107E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>170</v>
       </c>
@@ -8689,7 +9183,7 @@
         <v>2.25</v>
       </c>
       <c r="AP37" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-0.38235294117647067</v>
       </c>
       <c r="AQ37" s="13">
@@ -8755,12 +9249,26 @@
         <f t="shared" si="16"/>
         <v>-0.23636363636363625</v>
       </c>
-      <c r="BI37" s="8">
+      <c r="BI37" s="13">
+        <v>1.6000000000000003</v>
+      </c>
+      <c r="BJ37" s="7">
         <f t="shared" si="17"/>
-        <v>-0.56701030927835039</v>
+        <v>-0.23809523809523811</v>
+      </c>
+      <c r="BK37" s="13">
+        <v>1.1428571428571426</v>
+      </c>
+      <c r="BL37" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.28571428571428598</v>
+      </c>
+      <c r="BM37" s="8">
+        <f t="shared" si="19"/>
+        <v>-0.76435935198821792</v>
       </c>
     </row>
-    <row r="38" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>171</v>
       </c>
@@ -8902,7 +9410,7 @@
         <v>5.5999999999999979</v>
       </c>
       <c r="AP38" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.2727272727272721</v>
       </c>
       <c r="AQ38" s="13">
@@ -8968,12 +9476,26 @@
         <f t="shared" si="16"/>
         <v>-5.1117910096492664E-2</v>
       </c>
-      <c r="BI38" s="8">
+      <c r="BI38" s="13">
+        <v>5.1413793103448295</v>
+      </c>
+      <c r="BJ38" s="7">
         <f t="shared" si="17"/>
-        <v>2.4413793103448427E-2</v>
+        <v>3.7700282752122405E-3</v>
+      </c>
+      <c r="BK38" s="13">
+        <v>4.9655172413793123</v>
+      </c>
+      <c r="BL38" s="7">
+        <f t="shared" si="18"/>
+        <v>-3.4205231388330051E-2</v>
+      </c>
+      <c r="BM38" s="8">
+        <f t="shared" si="19"/>
+        <v>-6.8965517241375094E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>172</v>
       </c>
@@ -9115,7 +9637,7 @@
         <v>435</v>
       </c>
       <c r="AP39" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1.5777777777777777</v>
       </c>
       <c r="AQ39" s="13">
@@ -9181,12 +9703,26 @@
         <f t="shared" si="16"/>
         <v>0.18867924528301885</v>
       </c>
-      <c r="BI39" s="8">
+      <c r="BI39" s="13">
+        <v>151.11111111111123</v>
+      </c>
+      <c r="BJ39" s="7">
         <f t="shared" si="17"/>
-        <v>3.2468619246861925</v>
+        <v>0.43915343915344013</v>
+      </c>
+      <c r="BK39" s="13">
+        <v>611</v>
+      </c>
+      <c r="BL39" s="7">
+        <f t="shared" si="18"/>
+        <v>3.0433823529411734</v>
+      </c>
+      <c r="BM39" s="8">
+        <f t="shared" si="19"/>
+        <v>23.712691771269174</v>
       </c>
     </row>
-    <row r="40" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>173</v>
       </c>
@@ -9328,7 +9864,7 @@
         <v>165</v>
       </c>
       <c r="AP40" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-3.7500000000000568E-2</v>
       </c>
       <c r="AQ40" s="13">
@@ -9394,12 +9930,26 @@
         <f t="shared" si="16"/>
         <v>0.38351254480286684</v>
       </c>
-      <c r="BI40" s="8">
+      <c r="BI40" s="13">
+        <v>133.75</v>
+      </c>
+      <c r="BJ40" s="7">
         <f t="shared" si="17"/>
-        <v>3.9434728846493541</v>
+        <v>0.24740932642487096</v>
+      </c>
+      <c r="BK40" s="13">
+        <v>621.42857142857122</v>
+      </c>
+      <c r="BL40" s="7">
+        <f t="shared" si="18"/>
+        <v>3.6461949265687563</v>
+      </c>
+      <c r="BM40" s="8">
+        <f t="shared" si="19"/>
+        <v>27.650919827390407</v>
       </c>
     </row>
-    <row r="41" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>174</v>
       </c>
@@ -9541,7 +10091,7 @@
         <v>1218.1875</v>
       </c>
       <c r="AP41" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>9.2522542831379617</v>
       </c>
       <c r="AQ41" s="13">
@@ -9607,12 +10157,26 @@
         <f t="shared" si="16"/>
         <v>-2.31607629427792E-2</v>
       </c>
-      <c r="BI41" s="8">
+      <c r="BI41" s="13">
+        <v>554.46428571428567</v>
+      </c>
+      <c r="BJ41" s="7">
         <f t="shared" si="17"/>
-        <v>6.5473684210526315</v>
+        <v>3.1081888822474469E-2</v>
+      </c>
+      <c r="BK41" s="13">
+        <v>408.26086956521743</v>
+      </c>
+      <c r="BL41" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.26368409997899589</v>
+      </c>
+      <c r="BM41" s="8">
+        <f t="shared" si="19"/>
+        <v>4.7299771167048057</v>
       </c>
     </row>
-    <row r="42" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>175</v>
       </c>
@@ -9649,7 +10213,7 @@
         <v>25</v>
       </c>
       <c r="L42" s="7">
-        <f t="shared" ref="L42:L44" si="19">(K42/I42*100-100)/100</f>
+        <f t="shared" ref="L42:L44" si="21">(K42/I42*100-100)/100</f>
         <v>1.9069767441860466</v>
       </c>
       <c r="M42" s="11">
@@ -9754,7 +10318,7 @@
         <v>50</v>
       </c>
       <c r="AP42" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>6.6666666666666707E-2</v>
       </c>
       <c r="AQ42" s="13">
@@ -9820,12 +10384,26 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BI42" s="8">
+      <c r="BI42" s="13">
+        <v>50</v>
+      </c>
+      <c r="BJ42" s="7">
         <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BK42" s="13">
+        <v>50</v>
+      </c>
+      <c r="BL42" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BM42" s="8">
+        <f t="shared" si="19"/>
         <v>4.8139534883720936</v>
       </c>
     </row>
-    <row r="43" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>176</v>
       </c>
@@ -9855,14 +10433,14 @@
         <v>14.6</v>
       </c>
       <c r="J43" s="7">
-        <f t="shared" ref="J43:J44" si="20">(I43/G43*100-100)/100</f>
+        <f t="shared" ref="J43:J44" si="22">(I43/G43*100-100)/100</f>
         <v>0</v>
       </c>
       <c r="K43" s="6">
         <v>50</v>
       </c>
       <c r="L43" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2.4246575342465753</v>
       </c>
       <c r="M43" s="11">
@@ -9967,7 +10545,7 @@
         <v>100</v>
       </c>
       <c r="AP43" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>6.6666666666666707E-2</v>
       </c>
       <c r="AQ43" s="13">
@@ -10033,12 +10611,26 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BI43" s="8">
+      <c r="BI43" s="13">
+        <v>100</v>
+      </c>
+      <c r="BJ43" s="7">
         <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BK43" s="13">
+        <v>100</v>
+      </c>
+      <c r="BL43" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BM43" s="8">
+        <f t="shared" si="19"/>
         <v>5.8493150684931505</v>
       </c>
     </row>
-    <row r="44" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>177</v>
       </c>
@@ -10068,14 +10660,14 @@
         <v>24</v>
       </c>
       <c r="J44" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K44" s="6">
         <v>100</v>
       </c>
       <c r="L44" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>3.166666666666667</v>
       </c>
       <c r="M44" s="11">
@@ -10180,7 +10772,7 @@
         <v>200</v>
       </c>
       <c r="AP44" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>6.6666666666666707E-2</v>
       </c>
       <c r="AQ44" s="13">
@@ -10246,12 +10838,26 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BI44" s="8">
+      <c r="BI44" s="13">
+        <v>200</v>
+      </c>
+      <c r="BJ44" s="7">
         <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BK44" s="13">
+        <v>200</v>
+      </c>
+      <c r="BL44" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BM44" s="8">
+        <f t="shared" si="19"/>
         <v>7.3333333333333339</v>
       </c>
     </row>
-    <row r="45" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>186</v>
       </c>
@@ -10363,7 +10969,7 @@
         <v>4.75</v>
       </c>
       <c r="AP45" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-0.11920529801324492</v>
       </c>
       <c r="AQ45" s="13">
@@ -10429,12 +11035,26 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BI45" s="16">
-        <f>(BG45/M45*100-100)/100</f>
-        <v>-0.74193548387096764</v>
+      <c r="BI45" s="13">
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="BJ45" s="7">
+        <f t="shared" si="17"/>
+        <v>-0.3928571428571429</v>
+      </c>
+      <c r="BK45" s="13">
+        <v>1.4545454545454546</v>
+      </c>
+      <c r="BL45" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.40106951871657748</v>
+      </c>
+      <c r="BM45" s="16">
+        <f>(BK45/M45*100-100)/100</f>
+        <v>-0.90615835777126097</v>
       </c>
     </row>
-    <row r="46" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>188</v>
       </c>
@@ -10545,7 +11165,7 @@
         <v>11.25</v>
       </c>
       <c r="AP46" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.42212189616252827</v>
       </c>
       <c r="AQ46" s="13">
@@ -10611,12 +11231,26 @@
         <f t="shared" si="16"/>
         <v>-6.3063063063063113E-2</v>
       </c>
-      <c r="BI46" s="16">
-        <f t="shared" ref="BI46:BI48" si="21">(BG46/M46*100-100)/100</f>
-        <v>-0.65333333333333343</v>
+      <c r="BI46" s="13">
+        <v>7.375</v>
+      </c>
+      <c r="BJ46" s="7">
+        <f t="shared" si="17"/>
+        <v>-0.14903846153846145</v>
+      </c>
+      <c r="BK46" s="13">
+        <v>8</v>
+      </c>
+      <c r="BL46" s="7">
+        <f t="shared" si="18"/>
+        <v>8.4745762711864361E-2</v>
+      </c>
+      <c r="BM46" s="16">
+        <f t="shared" ref="BM46:BM48" si="23">(BK46/M46*100-100)/100</f>
+        <v>-0.68</v>
       </c>
     </row>
-    <row r="47" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>190</v>
       </c>
@@ -10727,7 +11361,7 @@
         <v>62.777777777777779</v>
       </c>
       <c r="AP47" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.42241587993221968</v>
       </c>
       <c r="AQ47" s="13">
@@ -10793,12 +11427,26 @@
         <f t="shared" si="16"/>
         <v>-0.42587601078167109</v>
       </c>
-      <c r="BI47" s="16">
-        <f t="shared" si="21"/>
-        <v>-0.3660714285714286</v>
+      <c r="BI47" s="13">
+        <v>33.363636363636367</v>
+      </c>
+      <c r="BJ47" s="7">
+        <f t="shared" si="17"/>
+        <v>-0.34212548015364902</v>
+      </c>
+      <c r="BK47" s="13">
+        <v>34.117647058823529</v>
+      </c>
+      <c r="BL47" s="7">
+        <f t="shared" si="18"/>
+        <v>2.2599775605064848E-2</v>
+      </c>
+      <c r="BM47" s="16">
+        <f t="shared" si="23"/>
+        <v>-0.57352941176470584</v>
       </c>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>193</v>
       </c>
@@ -10909,7 +11557,7 @@
         <v>125.55555555555556</v>
       </c>
       <c r="AP48" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.42241587993221968</v>
       </c>
       <c r="AQ48" s="13">
@@ -10975,9 +11623,23 @@
         <f t="shared" si="16"/>
         <v>-0.42587601078167109</v>
       </c>
-      <c r="BI48" s="16">
-        <f t="shared" si="21"/>
-        <v>-0.3660714285714286</v>
+      <c r="BI48" s="13">
+        <v>66.727272727272734</v>
+      </c>
+      <c r="BJ48" s="7">
+        <f t="shared" si="17"/>
+        <v>-0.34212548015364902</v>
+      </c>
+      <c r="BK48" s="13">
+        <v>68.235294117647058</v>
+      </c>
+      <c r="BL48" s="7">
+        <f t="shared" si="18"/>
+        <v>2.2599775605064848E-2</v>
+      </c>
+      <c r="BM48" s="16">
+        <f t="shared" si="23"/>
+        <v>-0.57352941176470584</v>
       </c>
     </row>
   </sheetData>

--- a/data/Prices of basic commodities in Gaza/commodity-prices-in-gaza.xlsx
+++ b/data/Prices of basic commodities in Gaza/commodity-prices-in-gaza.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="220">
   <si>
     <t>أرز حبة طويلة الياسمين تايلند - 1 كغم</t>
   </si>
@@ -683,6 +683,15 @@
   </si>
   <si>
     <t>Monthly Percent Change % (January 2026 - February 2026)</t>
+  </si>
+  <si>
+    <t>Monthly Percent Change % (February 2026 - March 2026)</t>
+  </si>
+  <si>
+    <t>Monthly Percent Change % (March - April 2026)</t>
+  </si>
+  <si>
+    <t>Monthly Percent Change % (April - May 2026)</t>
   </si>
 </sst>
 </file>
@@ -1110,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:BM48"/>
+  <dimension ref="A2:BS48"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" style="5" customWidth="1"/>
@@ -1124,12 +1133,12 @@
     <col min="9" max="9" width="12.42578125" style="5" customWidth="1"/>
     <col min="10" max="10" width="19.140625" style="5" customWidth="1"/>
     <col min="11" max="11" width="18.42578125" style="5" customWidth="1"/>
-    <col min="12" max="64" width="20.85546875" style="5" customWidth="1"/>
-    <col min="65" max="65" width="20.42578125" style="5" customWidth="1"/>
-    <col min="66" max="16384" width="8.85546875" style="5"/>
+    <col min="12" max="70" width="20.85546875" style="5" customWidth="1"/>
+    <col min="71" max="71" width="20.42578125" style="5" customWidth="1"/>
+    <col min="72" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:65" s="1" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:71" s="1" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>98</v>
       </c>
@@ -1319,11 +1328,29 @@
       <c r="BL2" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BM2" s="3">
+        <v>46082</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="BO2" s="3">
+        <v>46113</v>
+      </c>
+      <c r="BP2" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="BQ2" s="3">
+        <v>46143</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="BS2" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>136</v>
       </c>
@@ -1545,12 +1572,33 @@
         <f>(BK3/BI3*100-100)/100</f>
         <v>0.47816039191788096</v>
       </c>
-      <c r="BM3" s="8">
-        <f>(BK3/F3*100-100)/100</f>
-        <v>0.20017057918057632</v>
+      <c r="BM3" s="13">
+        <v>12.274045384577182</v>
+      </c>
+      <c r="BN3" s="7">
+        <f>(BM3/BK3*100-100)/100</f>
+        <v>0.32348342881619119</v>
+      </c>
+      <c r="BO3" s="13">
+        <v>13.595865656762417</v>
+      </c>
+      <c r="BP3" s="7">
+        <f>(BO3/BM3*100-100)/100</f>
+        <v>0.10769230769230774</v>
+      </c>
+      <c r="BQ3" s="13">
+        <v>12.538409439014243</v>
+      </c>
+      <c r="BR3" s="7">
+        <f>(BQ3/BO3*100-100)/100</f>
+        <v>-7.7777777777776724E-2</v>
+      </c>
+      <c r="BS3" s="8">
+        <f>(BQ3/F3*100-100)/100</f>
+        <v>0.62261769210772544</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>137</v>
       </c>
@@ -1769,15 +1817,36 @@
         <v>62.169934640522911</v>
       </c>
       <c r="BL4" s="7">
-        <f t="shared" ref="BL4:BL48" si="18">(BK4/BI4*100-100)/100</f>
+        <f t="shared" ref="BL4:BR48" si="18">(BK4/BI4*100-100)/100</f>
         <v>2.2599775605064848E-2</v>
       </c>
-      <c r="BM4" s="8">
-        <f t="shared" ref="BM4:BM44" si="19">(BK4/F4*100-100)/100</f>
-        <v>-0.31681390504919876</v>
+      <c r="BM4" s="13">
+        <v>118.44444444444456</v>
+      </c>
+      <c r="BN4" s="7">
+        <f t="shared" si="18"/>
+        <v>0.90517241379310409</v>
+      </c>
+      <c r="BO4" s="13">
+        <v>182.22222222222231</v>
+      </c>
+      <c r="BP4" s="7">
+        <f t="shared" si="18"/>
+        <v>0.53846153846153788</v>
+      </c>
+      <c r="BQ4" s="13">
+        <v>151.42666666666676</v>
+      </c>
+      <c r="BR4" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.16899999999999993</v>
+      </c>
+      <c r="BS4" s="8">
+        <f t="shared" ref="BS4:BS44" si="19">(BQ4/F4*100-100)/100</f>
+        <v>0.66402930402930505</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>138</v>
       </c>
@@ -1999,12 +2068,33 @@
         <f t="shared" si="18"/>
         <v>-0.25</v>
       </c>
-      <c r="BM5" s="8">
+      <c r="BM5" s="13">
+        <v>7.038461538461549</v>
+      </c>
+      <c r="BN5" s="7">
+        <f t="shared" si="18"/>
+        <v>0.56410256410256665</v>
+      </c>
+      <c r="BO5" s="13">
+        <v>5.5000000000000027</v>
+      </c>
+      <c r="BP5" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.21857923497267834</v>
+      </c>
+      <c r="BQ5" s="13">
+        <v>9.5000000000000036</v>
+      </c>
+      <c r="BR5" s="7">
+        <f t="shared" si="18"/>
+        <v>0.72727272727272718</v>
+      </c>
+      <c r="BS5" s="8">
         <f t="shared" si="19"/>
-        <v>-0.3571428571428571</v>
+        <v>0.35714285714285782</v>
       </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>139</v>
       </c>
@@ -2226,12 +2316,33 @@
         <f t="shared" si="18"/>
         <v>7.5267050123254645E-2</v>
       </c>
-      <c r="BM6" s="8">
+      <c r="BM6" s="13">
+        <v>31.100000000000009</v>
+      </c>
+      <c r="BN6" s="7">
+        <f t="shared" si="18"/>
+        <v>0.28335625859697389</v>
+      </c>
+      <c r="BO6" s="13">
+        <v>27.333333333333329</v>
+      </c>
+      <c r="BP6" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.12111468381564876</v>
+      </c>
+      <c r="BQ6" s="13">
+        <v>26.666666666666671</v>
+      </c>
+      <c r="BR6" s="7">
+        <f t="shared" si="18"/>
+        <v>-2.4390243902438727E-2</v>
+      </c>
+      <c r="BS6" s="8">
         <f t="shared" si="19"/>
-        <v>0.51458333333333373</v>
+        <v>0.66666666666666685</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>140</v>
       </c>
@@ -2453,12 +2564,33 @@
         <f t="shared" si="18"/>
         <v>0.24629080118694247</v>
       </c>
-      <c r="BM7" s="8">
+      <c r="BM7" s="13">
+        <v>40</v>
+      </c>
+      <c r="BN7" s="7">
+        <f t="shared" si="18"/>
+        <v>0.33333333333333315</v>
+      </c>
+      <c r="BO7" s="13">
+        <v>40</v>
+      </c>
+      <c r="BP7" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ7" s="13">
+        <v>51</v>
+      </c>
+      <c r="BR7" s="7">
+        <f t="shared" si="18"/>
+        <v>0.27499999999999986</v>
+      </c>
+      <c r="BS7" s="8">
         <f t="shared" si="19"/>
-        <v>1.25</v>
+        <v>2.8250000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>141</v>
       </c>
@@ -2680,12 +2812,33 @@
         <f t="shared" si="18"/>
         <v>-8.3003952569169565E-2</v>
       </c>
-      <c r="BM8" s="8">
+      <c r="BM8" s="13">
+        <v>39.991218345197836</v>
+      </c>
+      <c r="BN8" s="7">
+        <f t="shared" si="18"/>
+        <v>0.7133620689655189</v>
+      </c>
+      <c r="BO8" s="13">
+        <v>40.551742160278756</v>
+      </c>
+      <c r="BP8" s="7">
+        <f t="shared" si="18"/>
+        <v>1.4016172506738088E-2</v>
+      </c>
+      <c r="BQ8" s="13">
+        <v>35.097414267375754</v>
+      </c>
+      <c r="BR8" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.13450292397660846</v>
+      </c>
+      <c r="BS8" s="8">
         <f t="shared" si="19"/>
-        <v>-0.23221096854635134</v>
+        <v>0.15452020616367604</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>142</v>
       </c>
@@ -2907,12 +3060,33 @@
         <f t="shared" si="18"/>
         <v>-4.6979865771811548E-2</v>
       </c>
-      <c r="BM9" s="8">
+      <c r="BM9" s="13">
+        <v>14.36363636363637</v>
+      </c>
+      <c r="BN9" s="7">
+        <f t="shared" si="18"/>
+        <v>1.2253521126760554</v>
+      </c>
+      <c r="BO9" s="13">
+        <v>14.076923076923082</v>
+      </c>
+      <c r="BP9" s="7">
+        <f t="shared" si="18"/>
+        <v>-1.9961051606621254E-2</v>
+      </c>
+      <c r="BQ9" s="13">
+        <v>11.8125</v>
+      </c>
+      <c r="BR9" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.16086065573770525</v>
+      </c>
+      <c r="BS9" s="8">
         <f t="shared" si="19"/>
-        <v>1.5188470066518867</v>
+        <v>3.6097560975609753</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>143</v>
       </c>
@@ -3134,12 +3308,33 @@
         <f t="shared" si="18"/>
         <v>-6.6267042783262731E-2</v>
       </c>
-      <c r="BM10" s="8">
+      <c r="BM10" s="13">
+        <v>14.83888888888889</v>
+      </c>
+      <c r="BN10" s="7">
+        <f t="shared" si="18"/>
+        <v>0.47936859595679804</v>
+      </c>
+      <c r="BO10" s="13">
+        <v>13.371428571428568</v>
+      </c>
+      <c r="BP10" s="7">
+        <f t="shared" si="18"/>
+        <v>-9.8892870513986542E-2</v>
+      </c>
+      <c r="BQ10" s="13">
+        <v>14.046875</v>
+      </c>
+      <c r="BR10" s="7">
+        <f t="shared" si="18"/>
+        <v>5.0514155982906317E-2</v>
+      </c>
+      <c r="BS10" s="8">
         <f t="shared" si="19"/>
-        <v>1.0575498575498585</v>
+        <v>1.8814102564102564</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>144</v>
       </c>
@@ -3361,12 +3556,33 @@
         <f t="shared" si="18"/>
         <v>-0.11764705882352927</v>
       </c>
-      <c r="BM11" s="8">
+      <c r="BM11" s="13">
+        <v>21.75</v>
+      </c>
+      <c r="BN11" s="7">
+        <f t="shared" si="18"/>
+        <v>1.1749999999999998</v>
+      </c>
+      <c r="BO11" s="13">
+        <v>13.75</v>
+      </c>
+      <c r="BP11" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.36781609195402298</v>
+      </c>
+      <c r="BQ11" s="13">
+        <v>12.800000000000006</v>
+      </c>
+      <c r="BR11" s="7">
+        <f t="shared" si="18"/>
+        <v>-6.9090909090908634E-2</v>
+      </c>
+      <c r="BS11" s="8">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>1.5600000000000012</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>145</v>
       </c>
@@ -3588,12 +3804,33 @@
         <f t="shared" si="18"/>
         <v>0.1523809523809527</v>
       </c>
-      <c r="BM12" s="8">
+      <c r="BM12" s="13">
+        <v>17.272727272727266</v>
+      </c>
+      <c r="BN12" s="7">
+        <f t="shared" si="18"/>
+        <v>0.57024793388429684</v>
+      </c>
+      <c r="BO12" s="13">
+        <v>12.866666666666672</v>
+      </c>
+      <c r="BP12" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.25508771929824503</v>
+      </c>
+      <c r="BQ12" s="13">
+        <v>11.307692307692315</v>
+      </c>
+      <c r="BR12" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.12116381028298108</v>
+      </c>
+      <c r="BS12" s="8">
         <f t="shared" si="19"/>
-        <v>1.838709677419355</v>
+        <v>1.9181141439205975</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>146</v>
       </c>
@@ -3815,12 +4052,33 @@
         <f t="shared" si="18"/>
         <v>0.10869565217391283</v>
       </c>
-      <c r="BM13" s="8">
+      <c r="BM13" s="13">
+        <v>17.63636363636363</v>
+      </c>
+      <c r="BN13" s="7">
+        <f t="shared" si="18"/>
+        <v>0.90196078431372428</v>
+      </c>
+      <c r="BO13" s="13">
+        <v>13.333333333333329</v>
+      </c>
+      <c r="BP13" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.24398625429553264</v>
+      </c>
+      <c r="BQ13" s="13">
+        <v>11.470588235294125</v>
+      </c>
+      <c r="BR13" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.13970588235294032</v>
+      </c>
+      <c r="BS13" s="8">
         <f t="shared" si="19"/>
-        <v>7.242424242424244</v>
+        <v>9.1960784313725554</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>147</v>
       </c>
@@ -4042,12 +4300,33 @@
         <f t="shared" si="18"/>
         <v>-0.29934541792547847</v>
       </c>
-      <c r="BM14" s="8">
+      <c r="BM14" s="13">
+        <v>50</v>
+      </c>
+      <c r="BN14" s="7">
+        <f t="shared" si="18"/>
+        <v>1.3715415019762842</v>
+      </c>
+      <c r="BO14" s="13">
+        <v>38.730769230769262</v>
+      </c>
+      <c r="BP14" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.22538461538461477</v>
+      </c>
+      <c r="BQ14" s="13">
+        <v>28.625</v>
+      </c>
+      <c r="BR14" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.26092353525322792</v>
+      </c>
+      <c r="BS14" s="8">
         <f t="shared" si="19"/>
-        <v>4.6222222222222227</v>
+        <v>6.6333333333333337</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>148</v>
       </c>
@@ -4269,12 +4548,33 @@
         <f t="shared" si="18"/>
         <v>-0.22362869198312268</v>
       </c>
-      <c r="BM15" s="8">
+      <c r="BM15" s="13">
+        <v>33.600000000000009</v>
+      </c>
+      <c r="BN15" s="7">
+        <f t="shared" si="18"/>
+        <v>1.1913043478260885</v>
+      </c>
+      <c r="BO15" s="13">
+        <v>23.076923076923084</v>
+      </c>
+      <c r="BP15" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.31318681318681313</v>
+      </c>
+      <c r="BQ15" s="13">
+        <v>25.666666666666657</v>
+      </c>
+      <c r="BR15" s="7">
+        <f t="shared" si="18"/>
+        <v>0.11222222222222157</v>
+      </c>
+      <c r="BS15" s="8">
         <f t="shared" si="19"/>
-        <v>2.8333333333333313</v>
+        <v>5.4166666666666643</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>149</v>
       </c>
@@ -4496,12 +4796,33 @@
         <f t="shared" si="18"/>
         <v>0.23873873873873919</v>
       </c>
-      <c r="BM16" s="8">
+      <c r="BM16" s="13">
+        <v>15.692307692307683</v>
+      </c>
+      <c r="BN16" s="7">
+        <f t="shared" si="18"/>
+        <v>0.88307692307692121</v>
+      </c>
+      <c r="BO16" s="13">
+        <v>12.100000000000005</v>
+      </c>
+      <c r="BP16" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.22892156862745011</v>
+      </c>
+      <c r="BQ16" s="13">
+        <v>14.307692307692317</v>
+      </c>
+      <c r="BR16" s="7">
+        <f t="shared" si="18"/>
+        <v>0.18245390972663728</v>
+      </c>
+      <c r="BS16" s="8">
         <f t="shared" si="19"/>
-        <v>4.3333333333333348</v>
+        <v>8.1569230769230838</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>150</v>
       </c>
@@ -4723,12 +5044,33 @@
         <f t="shared" si="18"/>
         <v>-3.2139093782928542E-2</v>
       </c>
-      <c r="BM17" s="8">
+      <c r="BM17" s="13">
+        <v>13.333333333333329</v>
+      </c>
+      <c r="BN17" s="7">
+        <f t="shared" si="18"/>
+        <v>3.151696606786424</v>
+      </c>
+      <c r="BO17" s="13">
+        <v>9.550000000000006</v>
+      </c>
+      <c r="BP17" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.28374999999999928</v>
+      </c>
+      <c r="BQ17" s="13">
+        <v>7.71875</v>
+      </c>
+      <c r="BR17" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.19175392670157124</v>
+      </c>
+      <c r="BS17" s="8">
         <f t="shared" si="19"/>
-        <v>-0.11405835543766543</v>
+        <v>1.1293103448275863</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>151</v>
       </c>
@@ -4950,12 +5292,33 @@
         <f t="shared" si="18"/>
         <v>8.2329317269076649E-2</v>
       </c>
-      <c r="BM18" s="8">
+      <c r="BM18" s="13">
+        <v>12.272727272727268</v>
+      </c>
+      <c r="BN18" s="7">
+        <f t="shared" si="18"/>
+        <v>2.0055658627087198</v>
+      </c>
+      <c r="BO18" s="13">
+        <v>8.733333333333329</v>
+      </c>
+      <c r="BP18" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.28839506172839507</v>
+      </c>
+      <c r="BQ18" s="13">
+        <v>7.9375</v>
+      </c>
+      <c r="BR18" s="7">
+        <f t="shared" si="18"/>
+        <v>-9.1125954198472817E-2</v>
+      </c>
+      <c r="BS18" s="8">
         <f t="shared" si="19"/>
-        <v>0.59349593495934871</v>
+        <v>2.0975609756097562</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>152</v>
       </c>
@@ -5177,12 +5540,33 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM19" s="8">
+      <c r="BM19" s="13">
+        <v>4</v>
+      </c>
+      <c r="BN19" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BO19" s="13">
+        <v>4</v>
+      </c>
+      <c r="BP19" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ19" s="13">
+        <v>4</v>
+      </c>
+      <c r="BR19" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS19" s="8">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>153</v>
       </c>
@@ -5404,12 +5788,33 @@
         <f t="shared" si="18"/>
         <v>-0.15680473372781079</v>
       </c>
-      <c r="BM20" s="8">
+      <c r="BM20" s="13">
+        <v>81</v>
+      </c>
+      <c r="BN20" s="7">
+        <f t="shared" si="18"/>
+        <v>0.1084210526315789</v>
+      </c>
+      <c r="BO20" s="13">
+        <v>85</v>
+      </c>
+      <c r="BP20" s="7">
+        <f t="shared" si="18"/>
+        <v>4.9382716049382651E-2</v>
+      </c>
+      <c r="BQ20" s="13">
+        <v>85</v>
+      </c>
+      <c r="BR20" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS20" s="8">
         <f t="shared" si="19"/>
-        <v>9.762433442845813</v>
+        <v>11.518409425625919</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>154</v>
       </c>
@@ -5631,12 +6036,33 @@
         <f t="shared" si="18"/>
         <v>-0.11754742547425451</v>
       </c>
-      <c r="BM21" s="8">
+      <c r="BM21" s="13">
+        <v>34.333333333333336</v>
+      </c>
+      <c r="BN21" s="7">
+        <f t="shared" si="18"/>
+        <v>0.18618042226487502</v>
+      </c>
+      <c r="BO21" s="13">
+        <v>35</v>
+      </c>
+      <c r="BP21" s="7">
+        <f t="shared" si="18"/>
+        <v>1.9417475728155296E-2</v>
+      </c>
+      <c r="BQ21" s="13">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="BR21" s="7">
+        <f t="shared" si="18"/>
+        <v>-6.2857142857142917E-2</v>
+      </c>
+      <c r="BS21" s="8">
         <f t="shared" si="19"/>
-        <v>3.4598527649375113</v>
+        <v>4.0539291217257309</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>155</v>
       </c>
@@ -5858,12 +6284,33 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM22" s="8">
+      <c r="BM22" s="13">
+        <v>10</v>
+      </c>
+      <c r="BN22" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BO22" s="13">
+        <v>10</v>
+      </c>
+      <c r="BP22" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ22" s="13">
+        <v>10</v>
+      </c>
+      <c r="BR22" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS22" s="8">
         <f t="shared" si="19"/>
         <v>1.5</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>156</v>
       </c>
@@ -6085,12 +6532,33 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM23" s="8">
+      <c r="BM23" s="13">
+        <v>18</v>
+      </c>
+      <c r="BN23" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BO23" s="13">
+        <v>18</v>
+      </c>
+      <c r="BP23" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ23" s="13">
+        <v>18</v>
+      </c>
+      <c r="BR23" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS23" s="8">
         <f t="shared" si="19"/>
         <v>1.25</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>157</v>
       </c>
@@ -6312,12 +6780,33 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM24" s="8">
+      <c r="BM24" s="13">
+        <v>28</v>
+      </c>
+      <c r="BN24" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BO24" s="13">
+        <v>28</v>
+      </c>
+      <c r="BP24" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ24" s="13">
+        <v>28</v>
+      </c>
+      <c r="BR24" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS24" s="8">
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>158</v>
       </c>
@@ -6539,12 +7028,33 @@
         <f t="shared" si="18"/>
         <v>-8.1632653061223831E-2</v>
       </c>
-      <c r="BM25" s="8">
+      <c r="BM25" s="13">
+        <v>6.3333333333333268</v>
+      </c>
+      <c r="BN25" s="7">
+        <f t="shared" si="18"/>
+        <v>-1.4814814814816515E-2</v>
+      </c>
+      <c r="BO25" s="13">
+        <v>6</v>
+      </c>
+      <c r="BP25" s="7">
+        <f t="shared" si="18"/>
+        <v>-5.2631578947367502E-2</v>
+      </c>
+      <c r="BQ25" s="13">
+        <v>6</v>
+      </c>
+      <c r="BR25" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS25" s="8">
         <f t="shared" si="19"/>
-        <v>0.60714285714285832</v>
+        <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>159</v>
       </c>
@@ -6766,12 +7276,33 @@
         <f t="shared" si="18"/>
         <v>-0.1428571428571429</v>
       </c>
-      <c r="BM26" s="8">
+      <c r="BM26" s="13">
+        <v>6</v>
+      </c>
+      <c r="BN26" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BO26" s="13">
+        <v>6</v>
+      </c>
+      <c r="BP26" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ26" s="13">
+        <v>6</v>
+      </c>
+      <c r="BR26" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS26" s="8">
         <f t="shared" si="19"/>
         <v>-0.32035398230088502</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>160</v>
       </c>
@@ -6993,12 +7524,33 @@
         <f t="shared" si="18"/>
         <v>7.4705111402359414E-2</v>
       </c>
-      <c r="BM27" s="8">
+      <c r="BM27" s="13">
+        <v>156.57998790528913</v>
+      </c>
+      <c r="BN27" s="7">
+        <f t="shared" si="18"/>
+        <v>0.20731707317073186</v>
+      </c>
+      <c r="BO27" s="13">
+        <v>129.58707416538749</v>
+      </c>
+      <c r="BP27" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.17239057239057204</v>
+      </c>
+      <c r="BQ27" s="13">
+        <v>131.01052860089004</v>
+      </c>
+      <c r="BR27" s="7">
+        <f t="shared" si="18"/>
+        <v>1.098454027664701E-2</v>
+      </c>
+      <c r="BS27" s="8">
         <f t="shared" si="19"/>
-        <v>1.8472560973585928</v>
+        <v>1.8761916268032939</v>
       </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>161</v>
       </c>
@@ -7220,12 +7772,33 @@
         <f t="shared" si="18"/>
         <v>7.4705111402359137E-2</v>
       </c>
-      <c r="BM28" s="8">
+      <c r="BM28" s="13">
+        <v>173.28185328185327</v>
+      </c>
+      <c r="BN28" s="7">
+        <f t="shared" si="18"/>
+        <v>0.20731707317073172</v>
+      </c>
+      <c r="BO28" s="13">
+        <v>143.40969540969539</v>
+      </c>
+      <c r="BP28" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.17239057239057246</v>
+      </c>
+      <c r="BQ28" s="13">
+        <v>144.98498498498498</v>
+      </c>
+      <c r="BR28" s="7">
+        <f t="shared" si="18"/>
+        <v>1.0984540276647721E-2</v>
+      </c>
+      <c r="BS28" s="8">
         <f t="shared" si="19"/>
-        <v>1.5578959440345574</v>
+        <v>1.5838908215145835</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>162</v>
       </c>
@@ -7447,12 +8020,33 @@
         <f t="shared" si="18"/>
         <v>1.6652059596844709E-2</v>
       </c>
-      <c r="BM29" s="8">
+      <c r="BM29" s="13">
+        <v>40</v>
+      </c>
+      <c r="BN29" s="7">
+        <f t="shared" si="18"/>
+        <v>-4.868154158214992E-2</v>
+      </c>
+      <c r="BO29" s="13">
+        <v>40</v>
+      </c>
+      <c r="BP29" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ29" s="13">
+        <v>43.75</v>
+      </c>
+      <c r="BR29" s="7">
+        <f t="shared" si="18"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="BS29" s="8">
         <f t="shared" si="19"/>
-        <v>0.16437592258487754</v>
+        <v>0.21153846153846145</v>
       </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>163</v>
       </c>
@@ -7674,12 +8268,33 @@
         <f t="shared" si="18"/>
         <v>-2.0061728395062629E-2</v>
       </c>
-      <c r="BM30" s="8">
+      <c r="BM30" s="13">
+        <v>5</v>
+      </c>
+      <c r="BN30" s="7">
+        <f t="shared" si="18"/>
+        <v>-5.5118110236220305E-2</v>
+      </c>
+      <c r="BO30" s="13">
+        <v>4.875</v>
+      </c>
+      <c r="BP30" s="7">
+        <f t="shared" si="18"/>
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="BQ30" s="13">
+        <v>6.0749999999999966</v>
+      </c>
+      <c r="BR30" s="7">
+        <f t="shared" si="18"/>
+        <v>0.24615384615384556</v>
+      </c>
+      <c r="BS30" s="8">
         <f t="shared" si="19"/>
-        <v>0.36685116851168459</v>
+        <v>0.56918819188191805</v>
       </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>164</v>
       </c>
@@ -7901,12 +8516,33 @@
         <f t="shared" si="18"/>
         <v>-4.1322314049586736E-2</v>
       </c>
-      <c r="BM31" s="8">
+      <c r="BM31" s="13">
+        <v>50.000000000000014</v>
+      </c>
+      <c r="BN31" s="7">
+        <f t="shared" si="18"/>
+        <v>0.26436781609195409</v>
+      </c>
+      <c r="BO31" s="13">
+        <v>47.000000000000014</v>
+      </c>
+      <c r="BP31" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.06</v>
+      </c>
+      <c r="BQ31" s="13">
+        <v>40.000000000000014</v>
+      </c>
+      <c r="BR31" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.14893617021276598</v>
+      </c>
+      <c r="BS31" s="8">
         <f t="shared" si="19"/>
-        <v>0.11082737487231896</v>
+        <v>0.12359550561797789</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>165</v>
       </c>
@@ -8128,12 +8764,33 @@
         <f t="shared" si="18"/>
         <v>-9.7744360902255634E-2</v>
       </c>
-      <c r="BM32" s="8">
+      <c r="BM32" s="13">
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="BN32" s="7">
+        <f t="shared" si="18"/>
+        <v>0.2</v>
+      </c>
+      <c r="BO32" s="13">
+        <v>3</v>
+      </c>
+      <c r="BP32" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.125</v>
+      </c>
+      <c r="BQ32" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="BR32" s="7">
+        <f t="shared" si="18"/>
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="BS32" s="8">
         <f t="shared" si="19"/>
-        <v>0.90476190476190477</v>
+        <v>1.3333333333333335</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>166</v>
       </c>
@@ -8355,12 +9012,33 @@
         <f t="shared" si="18"/>
         <v>-2.7027027027027799E-2</v>
       </c>
-      <c r="BM33" s="8">
+      <c r="BM33" s="13">
+        <v>7.75</v>
+      </c>
+      <c r="BN33" s="7">
+        <f t="shared" si="18"/>
+        <v>0.29166666666666685</v>
+      </c>
+      <c r="BO33" s="13">
+        <v>8</v>
+      </c>
+      <c r="BP33" s="7">
+        <f t="shared" si="18"/>
+        <v>3.2258064516128969E-2</v>
+      </c>
+      <c r="BQ33" s="13">
+        <v>7.6000000000000085</v>
+      </c>
+      <c r="BR33" s="7">
+        <f t="shared" si="18"/>
+        <v>-4.9999999999998865E-2</v>
+      </c>
+      <c r="BS33" s="8">
         <f t="shared" si="19"/>
-        <v>6.4516129032257938E-2</v>
+        <v>0.34838709677419499</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>167</v>
       </c>
@@ -8582,12 +9260,33 @@
         <f t="shared" si="18"/>
         <v>-2.8732394366196842E-2</v>
       </c>
-      <c r="BM34" s="8">
+      <c r="BM34" s="13">
+        <v>126.5</v>
+      </c>
+      <c r="BN34" s="7">
+        <f t="shared" si="18"/>
+        <v>0.46751740139211079</v>
+      </c>
+      <c r="BO34" s="13">
+        <v>102</v>
+      </c>
+      <c r="BP34" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.19367588932806329</v>
+      </c>
+      <c r="BQ34" s="13">
+        <v>91.6</v>
+      </c>
+      <c r="BR34" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.10196078431372556</v>
+      </c>
+      <c r="BS34" s="8">
         <f t="shared" si="19"/>
-        <v>1.0486288848263259</v>
+        <v>1.1769652650822664</v>
       </c>
     </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>168</v>
       </c>
@@ -8809,12 +9508,33 @@
         <f t="shared" si="18"/>
         <v>-0.5</v>
       </c>
-      <c r="BM35" s="8">
+      <c r="BM35" s="13">
+        <v>1.9400000000000006</v>
+      </c>
+      <c r="BN35" s="7">
+        <f t="shared" si="18"/>
+        <v>0.36140350877192984</v>
+      </c>
+      <c r="BO35" s="13">
+        <v>1.4250000000000005</v>
+      </c>
+      <c r="BP35" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.26546391752577309</v>
+      </c>
+      <c r="BQ35" s="13">
+        <v>1.4250000000000005</v>
+      </c>
+      <c r="BR35" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS35" s="8">
         <f t="shared" si="19"/>
         <v>-0.61239999999999983</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>169</v>
       </c>
@@ -9036,12 +9756,33 @@
         <f t="shared" si="18"/>
         <v>-9.9781659388646207E-2</v>
       </c>
-      <c r="BM36" s="8">
+      <c r="BM36" s="13">
+        <v>2.6819444444444431</v>
+      </c>
+      <c r="BN36" s="7">
+        <f t="shared" si="18"/>
+        <v>0.21423630761491566</v>
+      </c>
+      <c r="BO36" s="13">
+        <v>3</v>
+      </c>
+      <c r="BP36" s="7">
+        <f t="shared" si="18"/>
+        <v>0.11859140341791871</v>
+      </c>
+      <c r="BQ36" s="13">
+        <v>2.9000000000000021</v>
+      </c>
+      <c r="BR36" s="7">
+        <f t="shared" si="18"/>
+        <v>-3.3333333333332715E-2</v>
+      </c>
+      <c r="BS36" s="8">
         <f t="shared" si="19"/>
-        <v>-1.5790155440415107E-2</v>
+        <v>0.29222797927461241</v>
       </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>170</v>
       </c>
@@ -9263,12 +10004,33 @@
         <f t="shared" si="18"/>
         <v>-0.28571428571428598</v>
       </c>
-      <c r="BM37" s="8">
+      <c r="BM37" s="13">
+        <v>1.1999999999999997</v>
+      </c>
+      <c r="BN37" s="7">
+        <f t="shared" si="18"/>
+        <v>0.05</v>
+      </c>
+      <c r="BO37" s="13">
+        <v>1</v>
+      </c>
+      <c r="BP37" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.16666666666666657</v>
+      </c>
+      <c r="BQ37" s="13">
+        <v>1.3333333333333328</v>
+      </c>
+      <c r="BR37" s="7">
+        <f t="shared" si="18"/>
+        <v>0.33333333333333287</v>
+      </c>
+      <c r="BS37" s="8">
         <f t="shared" si="19"/>
-        <v>-0.76435935198821792</v>
+        <v>-0.72508591065292105</v>
       </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>171</v>
       </c>
@@ -9490,12 +10252,33 @@
         <f t="shared" si="18"/>
         <v>-3.4205231388330051E-2</v>
       </c>
-      <c r="BM38" s="8">
+      <c r="BM38" s="13">
+        <v>4.8275862068965534</v>
+      </c>
+      <c r="BN38" s="7">
+        <f t="shared" si="18"/>
+        <v>-2.7777777777777856E-2</v>
+      </c>
+      <c r="BO38" s="13">
+        <v>4.8275862068965534</v>
+      </c>
+      <c r="BP38" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ38" s="13">
+        <v>4.8275862068965534</v>
+      </c>
+      <c r="BR38" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS38" s="8">
         <f t="shared" si="19"/>
-        <v>-6.8965517241375094E-3</v>
+        <v>-3.4482758620689252E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>172</v>
       </c>
@@ -9717,12 +10500,33 @@
         <f t="shared" si="18"/>
         <v>3.0433823529411734</v>
       </c>
-      <c r="BM39" s="8">
+      <c r="BM39" s="13">
+        <v>600</v>
+      </c>
+      <c r="BN39" s="7">
+        <f t="shared" si="18"/>
+        <v>-1.800327332242219E-2</v>
+      </c>
+      <c r="BO39" s="13">
+        <v>588.88888888888891</v>
+      </c>
+      <c r="BP39" s="7">
+        <f t="shared" si="18"/>
+        <v>-1.8518518518518476E-2</v>
+      </c>
+      <c r="BQ39" s="13">
+        <v>571.4285714285711</v>
+      </c>
+      <c r="BR39" s="7">
+        <f t="shared" si="18"/>
+        <v>-2.9649595687332209E-2</v>
+      </c>
+      <c r="BS39" s="8">
         <f t="shared" si="19"/>
-        <v>23.712691771269174</v>
+        <v>22.112173739788787</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>173</v>
       </c>
@@ -9944,12 +10748,33 @@
         <f t="shared" si="18"/>
         <v>3.6461949265687563</v>
       </c>
-      <c r="BM40" s="8">
+      <c r="BM40" s="13">
+        <v>556.25</v>
+      </c>
+      <c r="BN40" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.1048850574712641</v>
+      </c>
+      <c r="BO40" s="13">
+        <v>533.3333333333336</v>
+      </c>
+      <c r="BP40" s="7">
+        <f t="shared" si="18"/>
+        <v>-4.119850187265868E-2</v>
+      </c>
+      <c r="BQ40" s="13">
+        <v>535.71428571428589</v>
+      </c>
+      <c r="BR40" s="7">
+        <f t="shared" si="18"/>
+        <v>4.4642857142855518E-3</v>
+      </c>
+      <c r="BS40" s="8">
         <f t="shared" si="19"/>
-        <v>27.650919827390407</v>
+        <v>23.699068816715886</v>
       </c>
     </row>
-    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>174</v>
       </c>
@@ -10171,12 +10996,33 @@
         <f t="shared" si="18"/>
         <v>-0.26368409997899589</v>
       </c>
-      <c r="BM41" s="8">
+      <c r="BM41" s="13">
+        <v>678.75</v>
+      </c>
+      <c r="BN41" s="7">
+        <f t="shared" si="18"/>
+        <v>0.66253993610223605</v>
+      </c>
+      <c r="BO41" s="13">
+        <v>592.80000000000007</v>
+      </c>
+      <c r="BP41" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.12662983425414354</v>
+      </c>
+      <c r="BQ41" s="13">
+        <v>729.69230769230774</v>
+      </c>
+      <c r="BR41" s="7">
+        <f t="shared" si="18"/>
+        <v>0.23092494549984438</v>
+      </c>
+      <c r="BS41" s="8">
         <f t="shared" si="19"/>
-        <v>4.7299771167048057</v>
+        <v>9.2412955465587068</v>
       </c>
     </row>
-    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>175</v>
       </c>
@@ -10398,12 +11244,33 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM42" s="8">
+      <c r="BM42" s="13">
+        <v>50</v>
+      </c>
+      <c r="BN42" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BO42" s="13">
+        <v>50</v>
+      </c>
+      <c r="BP42" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ42" s="13">
+        <v>50</v>
+      </c>
+      <c r="BR42" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS42" s="8">
         <f t="shared" si="19"/>
         <v>4.8139534883720936</v>
       </c>
     </row>
-    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>176</v>
       </c>
@@ -10625,12 +11492,33 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM43" s="8">
+      <c r="BM43" s="13">
+        <v>100</v>
+      </c>
+      <c r="BN43" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BO43" s="13">
+        <v>100</v>
+      </c>
+      <c r="BP43" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ43" s="13">
+        <v>100</v>
+      </c>
+      <c r="BR43" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS43" s="8">
         <f t="shared" si="19"/>
         <v>5.8493150684931505</v>
       </c>
     </row>
-    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>177</v>
       </c>
@@ -10852,12 +11740,33 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BM44" s="8">
+      <c r="BM44" s="13">
+        <v>200</v>
+      </c>
+      <c r="BN44" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BO44" s="13">
+        <v>200</v>
+      </c>
+      <c r="BP44" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BQ44" s="13">
+        <v>200</v>
+      </c>
+      <c r="BR44" s="7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BS44" s="8">
         <f t="shared" si="19"/>
         <v>7.3333333333333339</v>
       </c>
     </row>
-    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>186</v>
       </c>
@@ -11049,12 +11958,33 @@
         <f t="shared" si="18"/>
         <v>-0.40106951871657748</v>
       </c>
-      <c r="BM45" s="16">
-        <f>(BK45/M45*100-100)/100</f>
-        <v>-0.90615835777126097</v>
+      <c r="BM45" s="13">
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="BN45" s="7">
+        <f t="shared" si="18"/>
+        <v>-1.7857142857142919E-2</v>
+      </c>
+      <c r="BO45" s="13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="BP45" s="7">
+        <f t="shared" si="18"/>
+        <v>0.54</v>
+      </c>
+      <c r="BQ45" s="13">
+        <v>2</v>
+      </c>
+      <c r="BR45" s="7">
+        <f t="shared" si="18"/>
+        <v>-9.0909090909090939E-2</v>
+      </c>
+      <c r="BS45" s="16">
+        <f>(BQ45/M45*100-100)/100</f>
+        <v>-0.87096774193548387</v>
       </c>
     </row>
-    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>188</v>
       </c>
@@ -11245,12 +12175,33 @@
         <f t="shared" si="18"/>
         <v>8.4745762711864361E-2</v>
       </c>
-      <c r="BM46" s="16">
-        <f t="shared" ref="BM46:BM48" si="23">(BK46/M46*100-100)/100</f>
-        <v>-0.68</v>
+      <c r="BM46" s="13">
+        <v>8.125</v>
+      </c>
+      <c r="BN46" s="7">
+        <f t="shared" si="18"/>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="BO46" s="13">
+        <v>9</v>
+      </c>
+      <c r="BP46" s="7">
+        <f t="shared" si="18"/>
+        <v>0.10769230769230774</v>
+      </c>
+      <c r="BQ46" s="13">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="BR46" s="7">
+        <f t="shared" si="18"/>
+        <v>-7.777777777777771E-2</v>
+      </c>
+      <c r="BS46" s="16">
+        <f t="shared" ref="BS46:BS48" si="23">(BQ46/M46*100-100)/100</f>
+        <v>-0.66799999999999993</v>
       </c>
     </row>
-    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>190</v>
       </c>
@@ -11441,12 +12392,33 @@
         <f t="shared" si="18"/>
         <v>2.2599775605064848E-2</v>
       </c>
-      <c r="BM47" s="16">
+      <c r="BM47" s="13">
+        <v>65</v>
+      </c>
+      <c r="BN47" s="7">
+        <f t="shared" si="18"/>
+        <v>0.90517241379310354</v>
+      </c>
+      <c r="BO47" s="13">
+        <v>100</v>
+      </c>
+      <c r="BP47" s="7">
+        <f t="shared" si="18"/>
+        <v>0.53846153846153866</v>
+      </c>
+      <c r="BQ47" s="13">
+        <v>83.1</v>
+      </c>
+      <c r="BR47" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.16900000000000007</v>
+      </c>
+      <c r="BS47" s="16">
         <f t="shared" si="23"/>
-        <v>-0.57352941176470584</v>
+        <v>3.8749999999999861E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>193</v>
       </c>
@@ -11637,9 +12609,30 @@
         <f t="shared" si="18"/>
         <v>2.2599775605064848E-2</v>
       </c>
-      <c r="BM48" s="16">
+      <c r="BM48" s="13">
+        <v>130</v>
+      </c>
+      <c r="BN48" s="7">
+        <f t="shared" si="18"/>
+        <v>0.90517241379310354</v>
+      </c>
+      <c r="BO48" s="13">
+        <v>200</v>
+      </c>
+      <c r="BP48" s="7">
+        <f t="shared" si="18"/>
+        <v>0.53846153846153866</v>
+      </c>
+      <c r="BQ48" s="13">
+        <v>166.2</v>
+      </c>
+      <c r="BR48" s="7">
+        <f t="shared" si="18"/>
+        <v>-0.16900000000000007</v>
+      </c>
+      <c r="BS48" s="16">
         <f t="shared" si="23"/>
-        <v>-0.57352941176470584</v>
+        <v>3.8749999999999861E-2</v>
       </c>
     </row>
   </sheetData>
